--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Tassa sui rifiuti (TARI) (1).xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Tassa sui rifiuti (TARI) (1).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="106">
   <si>
     <r>
       <t xml:space="preserve">
@@ -76,13 +76,19 @@
     <t>Messaggi presenti in questo template</t>
   </si>
   <si>
-    <t>Dichiarazione di nuova occupazione immobile</t>
+    <t xml:space="preserve">Dichiarazione di occupazione </t>
   </si>
   <si>
-    <t>Avviso di pagamento TARI</t>
+    <t>Dichiarazione di occupazione: accolta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avviso di pagamento TARI </t>
   </si>
   <si>
     <t>Avviso di pagamento TARI: in scadenza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Istruzioni sul pagamento della rata </t>
   </si>
   <si>
     <t>Proroga scadenza del pagamento</t>
@@ -236,14 +242,20 @@
     </r>
   </si>
   <si>
+    <t>…voglio ricevere informazioni su come funziona la TARI nel Comune.</t>
+  </si>
+  <si>
     <t>…voglio ricevere conferma che la dichiarazione di occupazione è stata processata correttamente.</t>
+  </si>
+  <si>
+    <t>…voglio essere avvisato quando devo pagare la TARI.</t>
+  </si>
+  <si>
+    <t>…voglio ricevere un promemoria per i pagamenti in scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">…voglio essere avvisato quando devo pagare la TARI.
 ℹ️ In caso di pagamenti su più rate, consultare questa sezione del manuale dei servizi dedicata. (https://docs.pagopa.it/manuale-servizi/che-cosa-puo-fare-un-servizio-su-io/inviare-messaggi/messaggi-che-veicolano-un-pagamento/soluzioni-per-pagamenti-a-rate)</t>
-  </si>
-  <si>
-    <t>…voglio ricevere un promemoria per i pagamenti in scadenza.</t>
   </si>
   <si>
     <t>…voglio essere avvisato se la scadenza del pagamento è stata prorogata.</t>
@@ -288,7 +300,37 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>Dichiarazione di nuova occupazione immobile</t>
+      <t xml:space="preserve">Dichiarazione di </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;inizio/variazione&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> occupazione immobile</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>La tua dichiarazione è stata accolta</t>
     </r>
   </si>
   <si>
@@ -311,6 +353,17 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t>Hai un pagamento in scadenza</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>Nuovo pagamento</t>
     </r>
   </si>
   <si>
@@ -355,7 +408,54 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">Abbiamo ricevuto la tua dichiarazione di occupazione di un nuovo immobile. Ecco i dettagli:
+      <t xml:space="preserve">Ti diamo il benvenuto nel Comune di </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;Comune&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve">. 
+Ricevi questo messaggio perché potresti avere recentemente cambiato residenza, acquistato un immobile o sottoscritto un contratto di affitto. 
+Se non lo hai già fatto, effettua o aggiorna la tua dichiarazione di occupazione ai fini TARI (Tassa sui Rifiuti). Per farlo, [visita questo sito](URL).
+Inoltre, se vuoi conoscere meglio il servizio offerto [visita questo sito](URL).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve">Abbiamo ricevuto la tua dichiarazione di </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;inizio/variazione&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> occupazione di un immobile. Ecco i dettagli:
 </t>
     </r>
     <r>
@@ -505,7 +605,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> e relativo a </t>
+      <t xml:space="preserve"> e relativo alla </t>
     </r>
     <r>
       <rPr>
@@ -514,7 +614,41 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>&lt;causale&gt;</t>
+      <t>&lt;rata unica/prima rata/seconda rata&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> della Tassa sui rifiuti (TARI) per l'immobile situato in </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;indirizzo&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;piano ed interno immobile&gt;</t>
     </r>
     <r>
       <rPr>
@@ -593,7 +727,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -624,6 +758,103 @@
       </rPr>
       <t xml:space="preserve"> sta per scadere.
 Se hai già provveduto a pagare l’avviso, ignora questo messaggio.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve">Dal </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;gg/mm/aaaa&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> sarà possibile pagare la Tassa sui rifiuti (TARI)  intestato a </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;nome cognome&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> per l'immobile situato in </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;indirizzo&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;piano ed interno immobile&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff448844"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>[Solo per messaggi Premium con allegato]</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> Trovi i pagamenti previsti in allegato a questo messaggio.
+Per avere maggiori informazioni sul pagamento, [visita il sito](URL).</t>
     </r>
   </si>
   <si>
@@ -771,6 +1002,9 @@
     <t>-</t>
   </si>
   <si>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
+  </si>
+  <si>
     <t>Vedi Avviso</t>
   </si>
   <si>
@@ -800,6 +1034,9 @@
     </r>
   </si>
   <si>
+    <t>&lt;documento con gli avvisi di pagamento delle rate previste&gt;</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -813,7 +1050,10 @@
     </r>
   </si>
   <si>
-    <t>I cittadini che hanno completato la dichiarazione di occupazione di un immobile.</t>
+    <t>I cittadini che hanno recentemente cambiato residenza, acquistato un immobile o completato un contratto di affitto superiore a sei mesi.</t>
+  </si>
+  <si>
+    <t>I cittadini che hanno completato la dichiarazione di inizio o variazione occupazione di un immobile.</t>
   </si>
   <si>
     <t>Tutti i cittadini residenti nell’area geografica di azione del servizio che devono pagare la TARI.</t>
@@ -835,7 +1075,10 @@
     </r>
   </si>
   <si>
-    <t>Alla conclusione della registrazione dell'immobile a nome del cittadino.</t>
+    <t>Quando l'ente riscontra aggiornamenti su cambi residenza, acquisto immobili o contratti d'affitto.</t>
+  </si>
+  <si>
+    <t>Alla conclusione della registrazione della dichiarazione.</t>
   </si>
   <si>
     <t>Al momento in cui l'avviso è pagabile da parte del cittadino.</t>
@@ -861,6 +1104,10 @@
     <t xml:space="preserve">Promemoria automatici — Messaggi Premium
 Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
 Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
+Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
   </si>
 </sst>
 </file>
@@ -1422,16 +1669,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="6" width="35" customWidth="1"/>
+    <col min="2" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>9</v>
@@ -1448,205 +1695,271 @@
       <c r="F1" s="33" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>55</v>
-      </c>
       <c r="C7" s="34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>55</v>
+        <v>105</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1673,7 +1986,7 @@
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -1703,10 +2016,10 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
@@ -1736,10 +2049,10 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1769,10 +2082,10 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
@@ -1802,10 +2115,10 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -1835,13 +2148,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="22"/>
@@ -1870,10 +2183,10 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
@@ -1903,13 +2216,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
@@ -1938,13 +2251,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26"/>
@@ -1973,10 +2286,10 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
@@ -2006,10 +2319,10 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
@@ -2039,10 +2352,10 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
@@ -2072,10 +2385,10 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
@@ -2105,10 +2418,10 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
@@ -2138,10 +2451,10 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -2171,10 +2484,10 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
@@ -2204,10 +2517,10 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -2237,10 +2550,10 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" s="29"/>
       <c r="D18" s="29"/>
@@ -2270,10 +2583,10 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C19" s="22"/>
       <c r="D19" s="22"/>
@@ -2303,7 +2616,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="30"/>
@@ -30779,11 +31092,15 @@
     </row>
     <row r="18" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
+      <c r="B18" s="11" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="19" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
-      <c r="B19" s="10"/>
+      <c r="B19" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="20" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
@@ -30989,8 +31306,10 @@
     <hyperlink ref="B15" r:id="rId4" tooltip="Vai al template del messaggio" location="#'Template messaggi'!D1"/>
     <hyperlink ref="B16" r:id="rId5" tooltip="Vai al template del messaggio" location="#'Template messaggi'!E1"/>
     <hyperlink ref="B17" r:id="rId6" tooltip="Vai al template del messaggio" location="#'Template messaggi'!F1"/>
+    <hyperlink ref="B18" r:id="rId7" tooltip="Vai al template del messaggio" location="#'Template messaggi'!G1"/>
+    <hyperlink ref="B19" r:id="rId8" tooltip="Vai al template del messaggio" location="#'Template messaggi'!H1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId7"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>